--- a/data/trans_orig/IP16B02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B02-Clase-trans_orig.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>27094</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27117</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45532</t>
+          <t>45600</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53367</t>
+          <t>53335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74887</t>
+          <t>75890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85961</t>
+          <t>85892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18685</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>15923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>22545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24788</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>37847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46457</t>
+          <t>46208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14764</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22297</t>
+          <t>22405</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29406</t>
+          <t>29770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57699</t>
+          <t>57448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68691</t>
+          <t>68653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>58014</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>66945</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119079</t>
+          <t>118563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133101</t>
+          <t>133257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20588</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30284</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>12614</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28974</t>
+          <t>28859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35024</t>
+          <t>34890</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22068</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43986</t>
+          <t>44682</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53514</t>
+          <t>53573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>39439</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46745</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87262</t>
+          <t>87110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98620</t>
+          <t>98914</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>14370</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
